--- a/results/2026-10-16/台股動量股初步名單_20261016.xlsx
+++ b/results/2026-10-16/台股動量股初步名單_20261016.xlsx
@@ -1992,6 +1992,9 @@
     <t xml:space="preserve">電腦及週邊設備業</t>
   </si>
   <si>
+    <t xml:space="preserve">題材／籌碼型</t>
+  </si>
+  <si>
     <t xml:space="preserve">注意股、仍虧損</t>
   </si>
   <si>
@@ -2614,9 +2617,6 @@
   </si>
   <si>
     <t xml:space="preserve">電子零組件業</t>
-  </si>
-  <si>
-    <t xml:space="preserve">題材／籌碼型</t>
   </si>
   <si>
     <r>
@@ -6007,7 +6007,24 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">＞ 去年同季，三項都符合＝基本面支持；否則＝題材／籌碼型</t>
+      <t xml:space="preserve">＞ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">且 ＞ 去年同季，全部符合＝基本面支持；否則＝題材／籌碼型</t>
     </r>
   </si>
   <si>
@@ -6529,7 +6546,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">濱川（</t>
+      <t xml:space="preserve">最近一季仍虧損的公司（例如濱川 </t>
     </r>
     <r>
       <rPr>
@@ -6546,24 +6563,24 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）依規則算「基本面支持」，但它仍在虧損，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">只是虧損比去年小，已加註「仍虧損」</t>
+      <t xml:space="preserve">）即使虧損縮小，也歸為題材／籌碼型（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-20 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">確認）</t>
     </r>
   </si>
   <si>
@@ -7600,11 +7617,11 @@
       <c r="E5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>36</v>
+      <c r="F5" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>78.9</v>
@@ -7681,13 +7698,13 @@
         <v>50.1903613706052</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AE5" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7695,10 +7712,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>34</v>
@@ -7785,13 +7802,13 @@
         <v>39.1581047826938</v>
       </c>
       <c r="AD6" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AE6" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AF6" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7799,19 +7816,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="6" t="n">
@@ -7912,7 +7929,7 @@
         <v>48</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>36</v>
@@ -8018,10 +8035,10 @@
         <v>34</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>81</v>
@@ -8124,10 +8141,10 @@
         <v>34</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>87</v>
@@ -8597,10 +8614,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="20" t="n">
         <v>5143796</v>
@@ -8644,10 +8661,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="20" t="n">
         <v>847235</v>
@@ -9072,7 +9089,7 @@
         <v>125</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>0.033210332103321</v>
@@ -9336,7 +9353,7 @@
         <v>142</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E12" s="26" t="n">
         <v>0.056047197640118</v>
@@ -9522,7 +9539,7 @@
         <v>153</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="26" t="n">
         <v>0.00343642611683848</v>
